--- a/education_forms/037_father_son_learning_survey--education_forms.xlsx
+++ b/education_forms/037_father_son_learning_survey--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Father Son Learning Survey</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Enter the title of the survey</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -548,10 +552,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Choose the category that best describes this survey</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -571,10 +579,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Briefly describe the purpose and objective of the survey</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -594,10 +606,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>father_son_learning_survey_hobbies</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Hobbies</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>What are some activities the father and son enjoy doing together?</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -607,47 +623,51 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>father_son_learning_survey_hobbies_other</t>
+          <t>father_son_learning_survey_conversation_topics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>other_hobbies</t>
+          <t>Conversation Topics</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Enter the other hobbies that you enjoy with your son</t>
+          <t>What subjects do the father and son usually discuss?</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>father_son_learning_survey_conversation_topics</t>
+          <t>father_son_learning_survey_reflections</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>conversation_topics</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Reflections</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>How often do you reflect on your relationship with your son?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>yes</t>
@@ -657,27 +677,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>father_son_learning_survey_conversation_topics_other</t>
+          <t>father_son_learning_survey_reflections_frequency</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>other_conversation_topics</t>
+          <t>Reflections Frequency</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Enter any other topics that you discuss with your son</t>
+          <t>How often do you take time to reflect on your relationship with your son?</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -689,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>father_son_learning_survey_reflections</t>
+          <t>father_son_learning_survey_suggestions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>reflections</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Suggestions</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>What are some suggestions for improving the father-son relationship?</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>yes</t>
@@ -707,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>father_son_learning_survey_recommendations</t>
+          <t>father_son_learning_survey_active_role</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>recommendations</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Active Role</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>How often do you take an active role in your son's education?</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>yes</t>
@@ -730,20 +758,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>father_son_learning_survey_reflections_on_reflections</t>
+          <t>father_son_learning_survey_education</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>What is your son's current level of education?</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>yes</t>
@@ -758,18 +790,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>father_son_learning_survey_recommendations_on_recommendations</t>
+          <t>father_son_learning_survey_other_hobbies</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>recommendations_on_recommendations</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Other Hobbies</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please specify any other activities you enjoy with your son</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -781,315 +817,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>father_son_learning_survey_reflections_on_reflections_on_reflections</t>
+          <t>father_son_learning_survey_other_topics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>reflections_on_reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Other Topics</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please specify any other subjects you discuss with your son</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>father_son_learning_survey_reflections_on_reflections_on_reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>reflections_on_reflections_on_reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>father_son_learning_survey_reflections_on_reflections_on_reflections_on_reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>reflections_on_reflections_on_reflections_on_reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>father_son_learning_survey_reflections_on_reflections_on_reflections_on_reflections_on_reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>reflections_on_reflections_on_reflections_on_reflections_on_reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>father_son_learning_survey_reflections_on_reflections_on_reflections_on_reflections_on_reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>reflections_on_reflections_on_reflections_on_reflections_on_reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>father_son_learning_survey_reflections_on_reflections_on_reflections_on_reflections_on_reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>reflections_on_reflections_on_reflections_on_reflections_on_reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>father_son_learning_survey_reflections_on_reflections_on_reflections_on_reflections_on_reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>reflections_on_reflections_on_reflections_on_reflections_on_reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>father_son_learning_survey_reflections_on_reflections_on_reflections_on_reflections_on_reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>reflections_on_reflections_on_reflections_on_reflections_on_reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>father_son_learning_survey_reflections_on_reflections_on_reflections_on_reflections_on_reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>reflections_on_reflections_on_reflections_on_reflections_on_reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>father_son_learning_survey_reflections_on_reflections_on_reflections_on_reflections_on_reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>reflections_on_reflections_on_reflections_on_reflections_on_reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>father_son_learning_survey_reflections_on_reflections_on_reflections_on_reflections_on_reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>reflections_on_reflections_on_reflections_on_reflections_on_reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>father_son_learning_survey_reflections_on_reflections_on_reflections_on_reflections_on_reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>reflections_on_reflections_on_reflections_on_reflections_on_reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>father_son_learning_survey_reflections_on_reflections_on_reflections_on_reflections_on_reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>reflections_on_reflections_on_reflections_on_reflections_on_reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>father_son_learning_survey_reflections_on_reflections_on_reflections_on_reflections_on_reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>reflections_on_reflections_on_reflections_on_reflections_on_reflections_on_reflections</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1106,12 +847,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +880,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>education_forms</t>
+          <t>personal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Education Forms</t>
+          <t>Personal</t>
         </is>
       </c>
     </row>
@@ -1156,46 +897,46 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>professional</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Professional</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>father_son_learning_survey_hobbies_choices</t>
+          <t>father_son_learning_survey_category_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>reading</t>
+          <t>educational</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>reading</t>
+          <t>Educational</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>father_son_learning_survey_hobbies_choices</t>
+          <t>father_son_learning_survey_category_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>playing_sports</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>playing sports</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1207,12 +948,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>playing_video_games</t>
+          <t>reading</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>playing video games</t>
+          <t>Reading</t>
         </is>
       </c>
     </row>
@@ -1224,12 +965,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>learning</t>
+          <t>sports</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>learning</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
@@ -1241,63 +982,63 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>playing_an_instrument</t>
+          <t>playing_video_games</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>playing an instrument</t>
+          <t>Playing Video Games</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>father_son_learning_survey_conversation_topics_choices</t>
+          <t>father_son_learning_survey_hobbies_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>schoolwork</t>
+          <t>playing_an_instrument</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>schoolwork</t>
+          <t>Playing an Instrument</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>father_son_learning_survey_conversation_topics_choices</t>
+          <t>father_son_learning_survey_hobbies_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>hobbies</t>
+          <t>learning</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hobbies</t>
+          <t>Learning</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>father_son_learning_survey_conversation_topics_choices</t>
+          <t>father_son_learning_survey_hobbies_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>interests</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>interests</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1050,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>goals</t>
+          <t>schoolwork</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>goals</t>
+          <t>Schoolwork</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1067,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>values</t>
+          <t>hobbies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>values</t>
+          <t>Hobbies</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1084,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>goals</t>
+          <t>interests</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>goals</t>
+          <t>Interests</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1101,386 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>goals</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Goals</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>father_son_learning_survey_conversation_topics_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>values</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>values</t>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>father_son_learning_survey_conversation_topics_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>father_son_learning_survey_reflections_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>father_son_learning_survey_reflections_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>father_son_learning_survey_reflections_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>father_son_learning_survey_reflections_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>father_son_learning_survey_reflections_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>father_son_learning_survey_reflections_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>10_minutes</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>10 minutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>father_son_learning_survey_reflections_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>30_minutes</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>30 minutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>father_son_learning_survey_reflections_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1_hour</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1 hour</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>father_son_learning_survey_reflections_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2_hours</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2 hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>father_son_learning_survey_reflections_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>more_than_2_hours</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>More than 2 hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>father_son_learning_survey_active_role_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>father_son_learning_survey_active_role_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>father_son_learning_survey_active_role_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>father_son_learning_survey_active_role_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>father_son_learning_survey_active_role_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>father_son_learning_survey_education_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>primary_school</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Primary School</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>father_son_learning_survey_education_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>secondary_school</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Secondary School</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>father_son_learning_survey_education_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>father_son_learning_survey_education_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>college</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>father_son_learning_survey_education_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
